--- a/C/Project/ATM_Sim/Doc/Project timeline.xlsx
+++ b/C/Project/ATM_Sim/Doc/Project timeline.xlsx
@@ -1,49 +1,361 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Embedded\C\Project\ATM_Sim\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hienm\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_F25DC773A252ABDACC104877291E53FE5BDE58E4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC28C30-23E8-4E42-BCDE-43E4BD4B851D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Timeline" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+  <si>
+    <t>ATM Machine - (V - Model)</t>
+  </si>
+  <si>
+    <t>Start: 14/09/2026 | End: 08/01/2027 | 17 weeks</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Tasks</t>
+  </si>
+  <si>
+    <t>Start day</t>
+  </si>
+  <si>
+    <t>End day</t>
+  </si>
+  <si>
+    <t>W1</t>
+  </si>
+  <si>
+    <t>W2</t>
+  </si>
+  <si>
+    <t>W3</t>
+  </si>
+  <si>
+    <t>W4</t>
+  </si>
+  <si>
+    <t>W5</t>
+  </si>
+  <si>
+    <t>W6</t>
+  </si>
+  <si>
+    <t>W7</t>
+  </si>
+  <si>
+    <t>W8</t>
+  </si>
+  <si>
+    <t>W9</t>
+  </si>
+  <si>
+    <t>W10</t>
+  </si>
+  <si>
+    <t>W11</t>
+  </si>
+  <si>
+    <t>W12</t>
+  </si>
+  <si>
+    <t>W13</t>
+  </si>
+  <si>
+    <t>W14</t>
+  </si>
+  <si>
+    <t>W15</t>
+  </si>
+  <si>
+    <t>W16</t>
+  </si>
+  <si>
+    <t>W17</t>
+  </si>
+  <si>
+    <t>14/09</t>
+  </si>
+  <si>
+    <t>21/09</t>
+  </si>
+  <si>
+    <t>28/09</t>
+  </si>
+  <si>
+    <t>19/10</t>
+  </si>
+  <si>
+    <t>26/10</t>
+  </si>
+  <si>
+    <t>16/11</t>
+  </si>
+  <si>
+    <t>23/11</t>
+  </si>
+  <si>
+    <t>30/11</t>
+  </si>
+  <si>
+    <t>14/12</t>
+  </si>
+  <si>
+    <t>21/12</t>
+  </si>
+  <si>
+    <t>28/12</t>
+  </si>
+  <si>
+    <t>Requirements &amp; Analysis</t>
+  </si>
+  <si>
+    <t>Gather user's need</t>
+  </si>
+  <si>
+    <t>14/09/2026</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
+    <t>System design</t>
+  </si>
+  <si>
+    <t>Login / Transfer / Withdraw / Balance)</t>
+  </si>
+  <si>
+    <t>Architecture design</t>
+  </si>
+  <si>
+    <t>Module design</t>
+  </si>
+  <si>
+    <t>Coding</t>
+  </si>
+  <si>
+    <t>Coding (C)</t>
+  </si>
+  <si>
+    <t>Review code</t>
+  </si>
+  <si>
+    <t>Unit testing</t>
+  </si>
+  <si>
+    <t>Integration</t>
+  </si>
+  <si>
+    <t>System testing</t>
+  </si>
+  <si>
+    <t>MS 1: SRS Approved</t>
+  </si>
+  <si>
+    <t>System description (critical features) and System requirement analysis</t>
+  </si>
+  <si>
+    <t>MS 2: Design Approved</t>
+  </si>
+  <si>
+    <t>30/10/2026</t>
+  </si>
+  <si>
+    <t>MS 3: Code Complete</t>
+  </si>
+  <si>
+    <t>Testing and Acceptance Testing</t>
+  </si>
+  <si>
+    <t>MS 4: Testing Complete</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d"/>
+  </numFmts>
+  <fonts count="17" x14ac:knownFonts="1">
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Corbel"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF1E2328"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF6B7280"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF6B7280"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF2B5FA5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Corbel"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF0E7C7B"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFF8F8F8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF3A3F47"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFB85B22"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFB4552B"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3A3F47"/>
+        <bgColor rgb="FF3A3F47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2B5FA5"/>
+        <bgColor rgb="FF2B5FA5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0E7C7B"/>
+        <bgColor rgb="FF0E7C7B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB4552B"/>
+        <bgColor rgb="FFB4552B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FF2B5FA5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FF3A3F47"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -51,12 +363,447 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -74,6 +821,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -85,39 +836,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -150,9 +901,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -185,6 +953,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -246,13 +1031,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -261,6 +1039,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -325,11 +1110,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -337,9 +1142,720 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:Y20"/>
+  <sheetFormatPr defaultColWidth="13.4609375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.765625" customWidth="1"/>
+    <col min="2" max="2" width="21.69140625" customWidth="1"/>
+    <col min="3" max="3" width="25.69140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.53515625" customWidth="1"/>
+    <col min="6" max="22" width="7.53515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:25" ht="18" x14ac:dyDescent="0.4">
+      <c r="A1" s="1"/>
+      <c r="B1" s="58" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2" s="4"/>
+      <c r="B2" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="3"/>
+      <c r="Y2" s="3"/>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" s="5"/>
+      <c r="B4" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="S4" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="T4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="U4" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="V4" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="W4" s="9"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" s="32">
+        <v>46152</v>
+      </c>
+      <c r="J5" s="16">
+        <v>46366</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="16">
+        <v>46064</v>
+      </c>
+      <c r="N5" s="16">
+        <v>46276</v>
+      </c>
+      <c r="O5" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R5" s="16">
+        <v>46215</v>
+      </c>
+      <c r="S5" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="T5" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="U5" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="V5" s="17">
+        <v>46113</v>
+      </c>
+      <c r="W5" s="9"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+    </row>
+    <row r="6" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="60">
+        <v>1</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" s="43"/>
+      <c r="G6" s="45" t="s">
+        <v>49</v>
+      </c>
+      <c r="H6" s="19"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="9"/>
+      <c r="X6" s="10"/>
+      <c r="Y6" s="10"/>
+    </row>
+    <row r="7" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="51"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="21"/>
+      <c r="Q7" s="21"/>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="9"/>
+      <c r="X7" s="10"/>
+      <c r="Y7" s="10"/>
+    </row>
+    <row r="8" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="63">
+        <v>2</v>
+      </c>
+      <c r="B8" s="64" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="37">
+        <v>46275</v>
+      </c>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="I8" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="P8" s="21"/>
+      <c r="Q8" s="21"/>
+      <c r="R8" s="21"/>
+      <c r="S8" s="21"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="9"/>
+      <c r="X8" s="10"/>
+      <c r="Y8" s="10"/>
+    </row>
+    <row r="9" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="51"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="P9" s="21"/>
+      <c r="Q9" s="21"/>
+      <c r="R9" s="21"/>
+      <c r="S9" s="21"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="9"/>
+      <c r="X9" s="10"/>
+      <c r="Y9" s="10"/>
+    </row>
+    <row r="10" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="51"/>
+      <c r="B10" s="53"/>
+      <c r="C10" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="P10" s="21"/>
+      <c r="Q10" s="21"/>
+      <c r="R10" s="21"/>
+      <c r="S10" s="21"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="9"/>
+      <c r="X10" s="10"/>
+      <c r="Y10" s="10"/>
+    </row>
+    <row r="11" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="50">
+        <v>3</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="37">
+        <v>46366</v>
+      </c>
+      <c r="E11" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="34"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="21"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="21"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="21"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="9"/>
+      <c r="X11" s="10"/>
+      <c r="Y11" s="10"/>
+    </row>
+    <row r="12" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="51"/>
+      <c r="B12" s="53"/>
+      <c r="C12" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="34"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="57"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="11"/>
+      <c r="O12" s="11"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="21"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="21"/>
+      <c r="T12" s="11"/>
+      <c r="U12" s="11"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="9"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+    </row>
+    <row r="13" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="65">
+        <v>4</v>
+      </c>
+      <c r="B13" s="66" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="37">
+        <v>46064</v>
+      </c>
+      <c r="E13" s="37">
+        <v>46214</v>
+      </c>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="O13" s="11"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="21"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="21"/>
+      <c r="T13" s="11"/>
+      <c r="U13" s="11"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="22"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+    </row>
+    <row r="14" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="51"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="67"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="34"/>
+      <c r="J14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="11"/>
+      <c r="U14" s="11"/>
+      <c r="V14" s="20"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+    </row>
+    <row r="15" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="51"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="36"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="28"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="21"/>
+      <c r="S15" s="21"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="20"/>
+      <c r="W15" s="22"/>
+      <c r="X15" s="10"/>
+      <c r="Y15" s="10"/>
+    </row>
+    <row r="16" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="23"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
+      <c r="K16" s="9"/>
+      <c r="L16" s="9"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
+      <c r="S16" s="9"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="9"/>
+      <c r="V16" s="9"/>
+      <c r="W16" s="9"/>
+      <c r="X16" s="10"/>
+      <c r="Y16" s="10"/>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17" s="23"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3"/>
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3"/>
+      <c r="O20" s="3"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3"/>
+      <c r="R20" s="3"/>
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+      <c r="U20" s="3"/>
+      <c r="V20" s="3"/>
+      <c r="W20" s="3"/>
+      <c r="X20" s="3"/>
+      <c r="Y20" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="I8:I10"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H8:H10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/C/Project/ATM_Sim/Doc/Project timeline.xlsx
+++ b/C/Project/ATM_Sim/Doc/Project timeline.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hienm\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Jira project\Embedded\C\Project\ATM_Sim\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDC28C30-23E8-4E42-BCDE-43E4BD4B851D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26013AA2-FE28-42F2-92B8-911427E01A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
   <si>
     <t>ATM Machine - (V - Model)</t>
   </si>
@@ -142,9 +142,6 @@
     <t>System design</t>
   </si>
   <si>
-    <t>Login / Transfer / Withdraw / Balance)</t>
-  </si>
-  <si>
     <t>Architecture design</t>
   </si>
   <si>
@@ -188,6 +185,15 @@
   </si>
   <si>
     <t>MS 4: Testing Complete</t>
+  </si>
+  <si>
+    <t>Ramp-up testing</t>
+  </si>
+  <si>
+    <t>Ramp-up-testing</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
   </si>
 </sst>
 </file>
@@ -305,7 +311,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -354,8 +360,14 @@
         <bgColor rgb="FF3A3F47"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -615,11 +627,81 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -664,9 +746,6 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -699,31 +778,65 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -747,61 +860,55 @@
     <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1145,7 +1252,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Y20"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultColWidth="13.4609375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.765625" customWidth="1"/>
@@ -1157,11 +1264,11 @@
   <sheetData>
     <row r="1" spans="1:25" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1186,11 +1293,11 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1263,7 +1370,7 @@
       <c r="H4" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="7" t="s">
         <v>9</v>
       </c>
       <c r="J4" s="7" t="s">
@@ -1324,7 +1431,7 @@
       <c r="H5" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="16">
         <v>46152</v>
       </c>
       <c r="J5" s="16">
@@ -1371,406 +1478,421 @@
       <c r="Y5" s="10"/>
     </row>
     <row r="6" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="60">
+      <c r="A6" s="44">
         <v>1</v>
       </c>
-      <c r="B6" s="61" t="s">
+      <c r="B6" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="45" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6" s="19"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
-      <c r="O6" s="19"/>
-      <c r="P6" s="19"/>
-      <c r="Q6" s="19"/>
-      <c r="R6" s="19"/>
-      <c r="S6" s="19"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="56" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="18"/>
+      <c r="R6" s="18"/>
+      <c r="S6" s="18"/>
       <c r="T6" s="11"/>
       <c r="U6" s="11"/>
-      <c r="V6" s="20"/>
+      <c r="V6" s="19"/>
       <c r="W6" s="9"/>
       <c r="X6" s="10"/>
       <c r="Y6" s="10"/>
     </row>
-    <row r="7" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="51"/>
-      <c r="B7" s="62"/>
-      <c r="C7" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="44"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="21"/>
-      <c r="L7" s="21"/>
-      <c r="M7" s="21"/>
-      <c r="N7" s="21"/>
-      <c r="O7" s="21"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
-      <c r="R7" s="21"/>
-      <c r="S7" s="21"/>
+    <row r="7" spans="1:25" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="20"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="20"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="20"/>
+      <c r="P7" s="20"/>
+      <c r="Q7" s="20"/>
+      <c r="R7" s="20"/>
+      <c r="S7" s="20"/>
       <c r="T7" s="11"/>
       <c r="U7" s="11"/>
-      <c r="V7" s="20"/>
+      <c r="V7" s="19"/>
       <c r="W7" s="9"/>
       <c r="X7" s="10"/>
       <c r="Y7" s="10"/>
     </row>
-    <row r="8" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="63">
-        <v>2</v>
-      </c>
-      <c r="B8" s="64" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="37" t="s">
+    <row r="8" spans="1:25" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="65"/>
+      <c r="B8" s="66"/>
+      <c r="C8" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="37">
+      <c r="E8" s="60">
         <v>46275</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="I8" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="21"/>
-      <c r="S8" s="21"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="60"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="59"/>
+      <c r="O8" s="59"/>
+      <c r="P8" s="20"/>
+      <c r="Q8" s="20"/>
+      <c r="R8" s="20"/>
+      <c r="S8" s="20"/>
       <c r="T8" s="11"/>
       <c r="U8" s="11"/>
-      <c r="V8" s="20"/>
+      <c r="V8" s="19"/>
       <c r="W8" s="9"/>
       <c r="X8" s="10"/>
       <c r="Y8" s="10"/>
     </row>
     <row r="9" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="51"/>
-      <c r="B9" s="62"/>
-      <c r="C9" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="21"/>
-      <c r="M9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
+      <c r="A9" s="46">
+        <v>2</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="70"/>
+      <c r="J9" s="51" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="65"/>
+      <c r="O9" s="65"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
       <c r="T9" s="11"/>
       <c r="U9" s="11"/>
-      <c r="V9" s="20"/>
+      <c r="V9" s="19"/>
       <c r="W9" s="9"/>
       <c r="X9" s="10"/>
       <c r="Y9" s="10"/>
     </row>
     <row r="10" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="51"/>
-      <c r="B10" s="53"/>
-      <c r="C10" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="49"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="21"/>
-      <c r="L10" s="21"/>
-      <c r="M10" s="21"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="21"/>
-      <c r="S10" s="21"/>
+      <c r="A10" s="63"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="25" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="52"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="65"/>
+      <c r="O10" s="65"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
       <c r="T10" s="11"/>
       <c r="U10" s="11"/>
-      <c r="V10" s="20"/>
+      <c r="V10" s="19"/>
       <c r="W10" s="9"/>
       <c r="X10" s="10"/>
       <c r="Y10" s="10"/>
     </row>
     <row r="11" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="50">
-        <v>3</v>
-      </c>
-      <c r="B11" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>44</v>
-      </c>
-      <c r="D11" s="37">
-        <v>46366</v>
-      </c>
-      <c r="E11" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="M11" s="21"/>
-      <c r="N11" s="11"/>
-      <c r="O11" s="11"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="21"/>
-      <c r="S11" s="21"/>
+      <c r="A11" s="63"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="53"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="65"/>
+      <c r="O11" s="65"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
       <c r="T11" s="11"/>
       <c r="U11" s="11"/>
-      <c r="V11" s="20"/>
+      <c r="V11" s="19"/>
       <c r="W11" s="9"/>
       <c r="X11" s="10"/>
       <c r="Y11" s="10"/>
     </row>
     <row r="12" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="51"/>
-      <c r="B12" s="53"/>
-      <c r="C12" s="18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="55"/>
-      <c r="K12" s="55"/>
-      <c r="L12" s="57"/>
-      <c r="M12" s="21"/>
+      <c r="A12" s="48">
+        <v>3</v>
+      </c>
+      <c r="B12" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="33">
+        <v>46366</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="40"/>
+      <c r="L12" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="M12" s="20"/>
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="21"/>
-      <c r="S12" s="21"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
       <c r="T12" s="11"/>
       <c r="U12" s="11"/>
-      <c r="V12" s="20"/>
+      <c r="V12" s="19"/>
       <c r="W12" s="9"/>
       <c r="X12" s="10"/>
       <c r="Y12" s="10"/>
     </row>
     <row r="13" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="65">
-        <v>4</v>
-      </c>
-      <c r="B13" s="66" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D13" s="37">
-        <v>46064</v>
-      </c>
-      <c r="E13" s="37">
-        <v>46214</v>
-      </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="29" t="s">
-        <v>55</v>
-      </c>
+      <c r="A13" s="63"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="11"/>
       <c r="O13" s="11"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
       <c r="T13" s="11"/>
       <c r="U13" s="11"/>
-      <c r="V13" s="20"/>
-      <c r="W13" s="22"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="9"/>
       <c r="X13" s="10"/>
       <c r="Y13" s="10"/>
     </row>
     <row r="14" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="51"/>
-      <c r="B14" s="62"/>
-      <c r="C14" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" s="67"/>
-      <c r="E14" s="38"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="21"/>
-      <c r="L14" s="21"/>
-      <c r="M14" s="28"/>
-      <c r="N14" s="30"/>
+      <c r="A14" s="30">
+        <v>4</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="33">
+        <v>46064</v>
+      </c>
+      <c r="E14" s="33">
+        <v>46214</v>
+      </c>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="65"/>
+      <c r="L14" s="20"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="28" t="s">
+        <v>54</v>
+      </c>
       <c r="O14" s="11"/>
-      <c r="P14" s="21"/>
-      <c r="Q14" s="21"/>
-      <c r="R14" s="21"/>
-      <c r="S14" s="21"/>
+      <c r="P14" s="20"/>
+      <c r="Q14" s="20"/>
+      <c r="R14" s="20"/>
+      <c r="S14" s="20"/>
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
-      <c r="V14" s="20"/>
-      <c r="W14" s="22"/>
+      <c r="V14" s="19"/>
+      <c r="W14" s="21"/>
       <c r="X14" s="10"/>
       <c r="Y14" s="10"/>
     </row>
     <row r="15" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="51"/>
-      <c r="B15" s="53"/>
-      <c r="C15" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="21"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="28"/>
-      <c r="N15" s="30"/>
+      <c r="A15" s="63"/>
+      <c r="B15" s="64"/>
+      <c r="C15" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="34"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="65"/>
+      <c r="L15" s="20"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="29"/>
       <c r="O15" s="11"/>
-      <c r="P15" s="21"/>
-      <c r="Q15" s="21"/>
-      <c r="R15" s="21"/>
-      <c r="S15" s="21"/>
+      <c r="P15" s="20"/>
+      <c r="Q15" s="20"/>
+      <c r="R15" s="20"/>
+      <c r="S15" s="20"/>
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
-      <c r="V15" s="20"/>
-      <c r="W15" s="22"/>
+      <c r="V15" s="19"/>
+      <c r="W15" s="21"/>
       <c r="X15" s="10"/>
       <c r="Y15" s="10"/>
     </row>
     <row r="16" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="23"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="9"/>
-      <c r="R16" s="9"/>
-      <c r="S16" s="9"/>
-      <c r="T16" s="9"/>
-      <c r="U16" s="9"/>
-      <c r="V16" s="9"/>
-      <c r="W16" s="9"/>
+      <c r="A16" s="63"/>
+      <c r="B16" s="68"/>
+      <c r="C16" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="35"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="27"/>
+      <c r="N16" s="29"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="20"/>
+      <c r="Q16" s="20"/>
+      <c r="R16" s="20"/>
+      <c r="S16" s="20"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="19"/>
+      <c r="W16" s="21"/>
       <c r="X16" s="10"/>
       <c r="Y16" s="10"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="23"/>
-      <c r="B17" s="25"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
+    <row r="17" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="22"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
+      <c r="K17" s="9"/>
+      <c r="L17" s="9"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
+      <c r="V17" s="9"/>
+      <c r="W17" s="9"/>
+      <c r="X17" s="10"/>
+      <c r="Y17" s="10"/>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
-      <c r="S18" s="3"/>
-      <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
@@ -1828,33 +1950,60 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+      <c r="N21" s="3"/>
+      <c r="O21" s="3"/>
+      <c r="P21" s="3"/>
+      <c r="Q21" s="3"/>
+      <c r="R21" s="3"/>
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+      <c r="U21" s="3"/>
+      <c r="V21" s="3"/>
+      <c r="W21" s="3"/>
+      <c r="X21" s="3"/>
+      <c r="Y21" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="J9:J11"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H9:I11"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:A10"/>
-    <mergeCell ref="B8:B10"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:B11"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="D8:D10"/>
-    <mergeCell ref="E8:E10"/>
-    <mergeCell ref="I8:I10"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H8:H10"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="J12:J13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/C/Project/ATM_Sim/Doc/Project timeline.xlsx
+++ b/C/Project/ATM_Sim/Doc/Project timeline.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Jira project\Embedded\C\Project\ATM_Sim\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26013AA2-FE28-42F2-92B8-911427E01A11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A789C046-0724-461D-BBB7-0CAFEE7400A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>ATM Machine - (V - Model)</t>
   </si>
@@ -193,7 +193,10 @@
     <t>Ramp-up-testing</t>
   </si>
   <si>
-    <t>16/10/2026</t>
+    <t>27/11/2026</t>
+  </si>
+  <si>
+    <t>30/11/2026</t>
   </si>
 </sst>
 </file>
@@ -367,7 +370,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -643,9 +646,60 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color rgb="FFCCCCCC"/>
       </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
         <color rgb="FFCCCCCC"/>
       </right>
@@ -658,50 +712,28 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
+      <left/>
       <right/>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -766,69 +798,117 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -836,79 +916,43 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="9" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1264,11 +1308,11 @@
   <sheetData>
     <row r="1" spans="1:25" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1293,11 +1337,11 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1478,23 +1522,23 @@
       <c r="Y5" s="10"/>
     </row>
     <row r="6" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="44">
+      <c r="A6" s="52">
         <v>1</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="54" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="50" t="s">
+      <c r="D6" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="50" t="s">
+      <c r="E6" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="54"/>
-      <c r="G6" s="56" t="s">
+      <c r="F6" s="39"/>
+      <c r="G6" s="41" t="s">
         <v>48</v>
       </c>
       <c r="H6" s="18"/>
@@ -1517,15 +1561,15 @@
       <c r="Y6" s="10"/>
     </row>
     <row r="7" spans="1:25" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="63"/>
-      <c r="B7" s="64"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="55"/>
       <c r="C7" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="35"/>
-      <c r="E7" s="35"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="57"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="42"/>
       <c r="H7" s="20"/>
       <c r="I7" s="20"/>
       <c r="J7" s="20"/>
@@ -1546,29 +1590,33 @@
       <c r="Y7" s="10"/>
     </row>
     <row r="8" spans="1:25" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="65"/>
-      <c r="B8" s="66"/>
-      <c r="C8" s="62" t="s">
+      <c r="A8" s="30"/>
+      <c r="B8" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="61" t="s">
+      <c r="D8" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="60">
+      <c r="E8" s="66">
         <v>46275</v>
       </c>
-      <c r="F8" s="58"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="60" t="s">
+      <c r="F8" s="26"/>
+      <c r="G8" s="31"/>
+      <c r="H8" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="60"/>
+      <c r="I8" s="68"/>
       <c r="J8" s="20"/>
       <c r="K8" s="20"/>
-      <c r="L8" s="20"/>
+      <c r="L8" s="70" t="s">
+        <v>50</v>
+      </c>
       <c r="M8" s="20"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="59"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
       <c r="P8" s="20"/>
       <c r="Q8" s="20"/>
       <c r="R8" s="20"/>
@@ -1581,34 +1629,28 @@
       <c r="Y8" s="10"/>
     </row>
     <row r="9" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="46">
+      <c r="A9" s="56">
         <v>2</v>
       </c>
-      <c r="B9" s="47" t="s">
-        <v>39</v>
-      </c>
+      <c r="B9" s="57"/>
       <c r="C9" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" s="33" t="s">
-        <v>57</v>
+      <c r="D9" s="34">
+        <v>46366</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>51</v>
       </c>
       <c r="F9" s="20"/>
       <c r="G9" s="20"/>
-      <c r="H9" s="69"/>
-      <c r="I9" s="70"/>
-      <c r="J9" s="51" t="s">
-        <v>50</v>
-      </c>
-      <c r="K9" s="20"/>
-      <c r="L9" s="20"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="44"/>
+      <c r="L9" s="37"/>
       <c r="M9" s="20"/>
-      <c r="N9" s="65"/>
-      <c r="O9" s="65"/>
-      <c r="P9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="30"/>
       <c r="Q9" s="20"/>
       <c r="R9" s="20"/>
       <c r="S9" s="20"/>
@@ -1620,24 +1662,22 @@
       <c r="Y9" s="10"/>
     </row>
     <row r="10" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="63"/>
-      <c r="B10" s="64"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
       <c r="F10" s="20"/>
       <c r="G10" s="20"/>
-      <c r="H10" s="71"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="52"/>
-      <c r="K10" s="20"/>
-      <c r="L10" s="20"/>
+      <c r="J10" s="45"/>
+      <c r="K10" s="46"/>
+      <c r="L10" s="37"/>
       <c r="M10" s="20"/>
-      <c r="N10" s="65"/>
-      <c r="O10" s="65"/>
-      <c r="P10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="30"/>
       <c r="Q10" s="20"/>
       <c r="R10" s="20"/>
       <c r="S10" s="20"/>
@@ -1649,24 +1689,22 @@
       <c r="Y10" s="10"/>
     </row>
     <row r="11" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="63"/>
-      <c r="B11" s="68"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="69"/>
       <c r="C11" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="37"/>
-      <c r="E11" s="37"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
       <c r="F11" s="20"/>
       <c r="G11" s="20"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="74"/>
-      <c r="J11" s="53"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="20"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="38"/>
       <c r="M11" s="20"/>
-      <c r="N11" s="65"/>
-      <c r="O11" s="65"/>
-      <c r="P11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="30"/>
       <c r="Q11" s="20"/>
       <c r="R11" s="20"/>
       <c r="S11" s="20"/>
@@ -1678,34 +1716,31 @@
       <c r="Y11" s="10"/>
     </row>
     <row r="12" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="48">
+      <c r="A12" s="64">
         <v>3</v>
       </c>
-      <c r="B12" s="49" t="s">
+      <c r="B12" s="65" t="s">
         <v>42</v>
       </c>
       <c r="C12" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="33">
-        <v>46366</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>51</v>
+      <c r="D12" s="34">
+        <v>46064</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>57</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="40"/>
-      <c r="L12" s="38" t="s">
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="M12" s="20"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="20"/>
       <c r="Q12" s="20"/>
       <c r="R12" s="20"/>
       <c r="S12" s="20"/>
@@ -1717,24 +1752,21 @@
       <c r="Y12" s="10"/>
     </row>
     <row r="13" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="63"/>
-      <c r="B13" s="68"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="58"/>
       <c r="C13" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="37"/>
-      <c r="E13" s="37"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
-      <c r="H13" s="20"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="41"/>
-      <c r="L13" s="39"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="20"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="M13" s="63"/>
+      <c r="N13" s="72"/>
+      <c r="O13" s="72"/>
+      <c r="P13" s="74"/>
       <c r="Q13" s="20"/>
       <c r="R13" s="20"/>
       <c r="S13" s="20"/>
@@ -1746,36 +1778,32 @@
       <c r="Y13" s="10"/>
     </row>
     <row r="14" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="30">
+      <c r="A14" s="59">
         <v>4</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="60" t="s">
         <v>53</v>
       </c>
       <c r="C14" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="33">
-        <v>46064</v>
-      </c>
-      <c r="E14" s="33">
-        <v>46214</v>
+      <c r="D14" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="E14" s="34">
+        <v>46338</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
       <c r="J14" s="20"/>
-      <c r="K14" s="65"/>
+      <c r="K14" s="20"/>
       <c r="L14" s="20"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="28" t="s">
+      <c r="M14" s="30"/>
+      <c r="N14" s="20"/>
+      <c r="Q14" s="75"/>
+      <c r="R14" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="O14" s="11"/>
-      <c r="P14" s="20"/>
-      <c r="Q14" s="20"/>
-      <c r="R14" s="20"/>
       <c r="S14" s="20"/>
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
@@ -1785,26 +1813,22 @@
       <c r="Y14" s="10"/>
     </row>
     <row r="15" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="63"/>
-      <c r="B15" s="64"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="55"/>
       <c r="C15" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="34"/>
-      <c r="E15" s="36"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
       <c r="F15" s="20"/>
       <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
       <c r="J15" s="20"/>
-      <c r="K15" s="65"/>
+      <c r="K15" s="20"/>
       <c r="L15" s="20"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="29"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="20"/>
-      <c r="R15" s="20"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="20"/>
+      <c r="Q15" s="76"/>
+      <c r="R15" s="78"/>
       <c r="S15" s="20"/>
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
@@ -1814,26 +1838,22 @@
       <c r="Y15" s="10"/>
     </row>
     <row r="16" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="63"/>
-      <c r="B16" s="68"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="35"/>
-      <c r="E16" s="37"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
       <c r="F16" s="20"/>
       <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
       <c r="J16" s="20"/>
-      <c r="K16" s="65"/>
+      <c r="K16" s="20"/>
       <c r="L16" s="20"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="20"/>
-      <c r="Q16" s="20"/>
-      <c r="R16" s="20"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="20"/>
+      <c r="Q16" s="76"/>
+      <c r="R16" s="78"/>
       <c r="S16" s="20"/>
       <c r="T16" s="11"/>
       <c r="U16" s="11"/>
@@ -1978,32 +1998,34 @@
       <c r="Y21" s="3"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="J9:J11"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H9:I11"/>
+  <mergeCells count="27">
+    <mergeCell ref="Q14:Q16"/>
+    <mergeCell ref="R14:R16"/>
+    <mergeCell ref="M12:O13"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="L8:L11"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:B11"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
-    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="J9:K11"/>
+    <mergeCell ref="H8:I8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/C/Project/ATM_Sim/Doc/Project timeline.xlsx
+++ b/C/Project/ATM_Sim/Doc/Project timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Jira project\Embedded\C\Project\ATM_Sim\Doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Embedded\C\Project\ATM_Sim\Doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A789C046-0724-461D-BBB7-0CAFEE7400A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3656517-49D8-428B-AC0D-664F4B61D3AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Timeline" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="65">
   <si>
     <t>ATM Machine - (V - Model)</t>
   </si>
@@ -142,18 +142,12 @@
     <t>System design</t>
   </si>
   <si>
-    <t>Architecture design</t>
-  </si>
-  <si>
     <t>Module design</t>
   </si>
   <si>
     <t>Coding</t>
   </si>
   <si>
-    <t>Coding (C)</t>
-  </si>
-  <si>
     <t>Review code</t>
   </si>
   <si>
@@ -197,6 +191,30 @@
   </si>
   <si>
     <t>30/11/2026</t>
+  </si>
+  <si>
+    <t>Test design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test case </t>
+  </si>
+  <si>
+    <t>Coding/ Testing</t>
+  </si>
+  <si>
+    <t>Test plan &amp; Test strategy</t>
+  </si>
+  <si>
+    <t>System / Architecture design</t>
+  </si>
+  <si>
+    <t>Coding (C) &amp; Review code</t>
+  </si>
+  <si>
+    <t>Fixing bug</t>
+  </si>
+  <si>
+    <t>Test case</t>
   </si>
 </sst>
 </file>
@@ -206,7 +224,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -252,12 +270,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF6B7280"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -310,6 +322,18 @@
     <font>
       <b/>
       <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -370,7 +394,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -380,7 +404,7 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF999999"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
         <color rgb="FFD9D9D9"/>
@@ -398,7 +422,7 @@
         <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="FFD9D9D9"/>
+        <color rgb="FF999999"/>
       </right>
       <top style="thin">
         <color rgb="FF999999"/>
@@ -413,103 +437,178 @@
         <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
         <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
         <color rgb="FF999999"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
         <color rgb="FF999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
         <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
       </left>
       <right/>
       <top/>
@@ -517,92 +616,81 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FF999999"/>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF999999"/>
       </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top/>
       <bottom/>
@@ -610,89 +698,148 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right/>
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
       <top/>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF999999"/>
-      </left>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="medium">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF999999"/>
-      </top>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
       <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
       <top style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFCCCCCC"/>
-      </left>
       <right/>
       <top style="medium">
         <color rgb="FF999999"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF999999"/>
+      </top>
       <bottom style="medium">
         <color rgb="FFCCCCCC"/>
       </bottom>
@@ -701,13 +848,150 @@
     <border>
       <left/>
       <right style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </right>
       <top style="medium">
-        <color rgb="FF999999"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </top>
       <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -715,25 +999,55 @@
       <left/>
       <right/>
       <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom/>
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -752,120 +1066,195 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -874,85 +1263,79 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="9" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="9" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -970,10 +1353,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1291,16 +1670,38 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="2">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{47C39DE5-2CA3-44B6-B1A6-4B8DE2804264}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;eb02fef3-3cfa-4d23-bf80-f229ee641a4a&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Y21"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr defaultColWidth="13.4609375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.765625" customWidth="1"/>
-    <col min="2" max="2" width="21.69140625" customWidth="1"/>
+    <col min="2" max="2" width="17.765625" customWidth="1"/>
     <col min="3" max="3" width="25.69140625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="10.53515625" customWidth="1"/>
     <col min="6" max="22" width="7.53515625" customWidth="1"/>
@@ -1308,11 +1709,11 @@
   <sheetData>
     <row r="1" spans="1:25" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1337,11 +1738,11 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1364,7 +1765,7 @@
       <c r="X2" s="3"/>
       <c r="Y2" s="3"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -1391,595 +1792,598 @@
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="5"/>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="K4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="7" t="s">
+      <c r="L4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="M4" s="7" t="s">
+      <c r="M4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N4" s="7" t="s">
+      <c r="N4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O4" s="7" t="s">
+      <c r="O4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="P4" s="7" t="s">
+      <c r="P4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="Q4" s="7" t="s">
+      <c r="Q4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="R4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="S4" s="7" t="s">
+      <c r="S4" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="T4" s="7" t="s">
+      <c r="T4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="U4" s="7" t="s">
+      <c r="U4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="V4" s="8" t="s">
+      <c r="V4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="W4" s="9"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="9"/>
+      <c r="Y4" s="9"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15" t="s">
+    <row r="5" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="32"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="I5" s="16">
+      <c r="I5" s="41">
         <v>46152</v>
       </c>
-      <c r="J5" s="16">
+      <c r="J5" s="41">
         <v>46366</v>
       </c>
-      <c r="K5" s="15" t="s">
+      <c r="K5" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="41">
         <v>46064</v>
       </c>
-      <c r="N5" s="16">
+      <c r="N5" s="41">
         <v>46276</v>
       </c>
-      <c r="O5" s="15" t="s">
+      <c r="O5" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="15" t="s">
+      <c r="P5" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="Q5" s="15" t="s">
+      <c r="Q5" s="40" t="s">
         <v>30</v>
       </c>
-      <c r="R5" s="16">
+      <c r="R5" s="41">
         <v>46215</v>
       </c>
-      <c r="S5" s="15" t="s">
+      <c r="S5" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="T5" s="15" t="s">
+      <c r="T5" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="U5" s="15" t="s">
+      <c r="U5" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="V5" s="17">
+      <c r="V5" s="42">
         <v>46113</v>
       </c>
-      <c r="W5" s="9"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="9"/>
+      <c r="Y5" s="9"/>
     </row>
-    <row r="6" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="52">
+    <row r="6" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="77">
         <v>1</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="79" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="39"/>
-      <c r="G6" s="41" t="s">
+      <c r="F6" s="70"/>
+      <c r="G6" s="72" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="10"/>
+      <c r="U6" s="10"/>
+      <c r="V6" s="12"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="9"/>
+      <c r="Y6" s="9"/>
+    </row>
+    <row r="7" spans="1:25" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="78"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="82"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="71"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
+      <c r="P7" s="13"/>
+      <c r="Q7" s="13"/>
+      <c r="R7" s="13"/>
+      <c r="S7" s="13"/>
+      <c r="T7" s="10"/>
+      <c r="U7" s="10"/>
+      <c r="V7" s="12"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="9"/>
+      <c r="Y7" s="9"/>
+    </row>
+    <row r="8" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="86">
+        <v>2</v>
+      </c>
+      <c r="B8" s="83" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="33">
+        <v>46275</v>
+      </c>
+      <c r="F8" s="26"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="I8" s="55"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
-      <c r="O6" s="18"/>
-      <c r="P6" s="18"/>
-      <c r="Q6" s="18"/>
-      <c r="R6" s="18"/>
-      <c r="S6" s="18"/>
-      <c r="T6" s="11"/>
-      <c r="U6" s="11"/>
-      <c r="V6" s="19"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="13"/>
+      <c r="Q8" s="13"/>
+      <c r="R8" s="13"/>
+      <c r="S8" s="13"/>
+      <c r="T8" s="10"/>
+      <c r="U8" s="10"/>
+      <c r="V8" s="12"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="9"/>
+      <c r="Y8" s="9"/>
     </row>
-    <row r="7" spans="1:25" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="53"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="25" t="s">
+    <row r="9" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="87"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="59">
+        <v>46366</v>
+      </c>
+      <c r="E9" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="42"/>
-      <c r="H7" s="20"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="20"/>
-      <c r="Q7" s="20"/>
-      <c r="R7" s="20"/>
-      <c r="S7" s="20"/>
-      <c r="T7" s="11"/>
-      <c r="U7" s="11"/>
-      <c r="V7" s="19"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="10"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="13"/>
+      <c r="J9" s="49" t="s">
+        <v>61</v>
+      </c>
+      <c r="K9" s="50"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="100"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="13"/>
+      <c r="R9" s="13"/>
+      <c r="S9" s="13"/>
+      <c r="T9" s="10"/>
+      <c r="U9" s="10"/>
+      <c r="V9" s="12"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="9"/>
+      <c r="Y9" s="9"/>
     </row>
-    <row r="8" spans="1:25" ht="44" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="30"/>
-      <c r="B8" s="57" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="29" t="s">
+    <row r="10" spans="1:25" ht="38" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="87"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="60"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="13"/>
+      <c r="K10" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="101"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="13"/>
+      <c r="R10" s="13"/>
+      <c r="S10" s="13"/>
+      <c r="T10" s="10"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="12"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="9"/>
+      <c r="Y10" s="9"/>
+    </row>
+    <row r="11" spans="1:25" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="87"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="60"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="13"/>
+      <c r="K11" s="49" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11" s="51"/>
+      <c r="M11" s="101"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="10"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="12"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="9"/>
+      <c r="Y11" s="9"/>
+    </row>
+    <row r="12" spans="1:25" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="88"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="61"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="13"/>
+      <c r="K12" s="52" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="53"/>
+      <c r="M12" s="101"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="12"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="9"/>
+      <c r="Y12" s="9"/>
+    </row>
+    <row r="13" spans="1:25" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="94">
+        <v>3</v>
+      </c>
+      <c r="B13" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="59">
+        <v>46064</v>
+      </c>
+      <c r="E13" s="59" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="66">
-        <v>46275</v>
-      </c>
-      <c r="F8" s="26"/>
-      <c r="G8" s="31"/>
-      <c r="H8" s="67" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" s="68"/>
-      <c r="J8" s="20"/>
-      <c r="K8" s="20"/>
-      <c r="L8" s="70" t="s">
+      <c r="F13" s="27"/>
+      <c r="G13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="11"/>
+      <c r="N13" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="O13" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="P13" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q13" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="20"/>
-      <c r="N8" s="27"/>
-      <c r="O8" s="27"/>
-      <c r="P8" s="20"/>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20"/>
-      <c r="T8" s="11"/>
-      <c r="U8" s="11"/>
-      <c r="V8" s="19"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10"/>
+      <c r="R13" s="13"/>
+      <c r="S13" s="13"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="12"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
     </row>
-    <row r="9" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="56">
-        <v>2</v>
-      </c>
-      <c r="B9" s="57"/>
-      <c r="C9" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="34">
-        <v>46366</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="20"/>
-      <c r="R9" s="20"/>
-      <c r="S9" s="20"/>
-      <c r="T9" s="11"/>
-      <c r="U9" s="11"/>
-      <c r="V9" s="19"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10"/>
+    <row r="14" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="95"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="K14" s="13"/>
+      <c r="N14" s="62" t="s">
+        <v>64</v>
+      </c>
+      <c r="O14" s="63"/>
+      <c r="P14" s="64"/>
+      <c r="Q14" s="47"/>
+      <c r="R14" s="13"/>
+      <c r="S14" s="13"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="12"/>
+      <c r="W14" s="8"/>
+      <c r="X14" s="9"/>
+      <c r="Y14" s="9"/>
     </row>
-    <row r="10" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="53"/>
-      <c r="B10" s="57"/>
-      <c r="C10" s="25" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="46"/>
-      <c r="L10" s="37"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="20"/>
-      <c r="R10" s="20"/>
-      <c r="S10" s="20"/>
-      <c r="T10" s="11"/>
-      <c r="U10" s="11"/>
-      <c r="V10" s="19"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10"/>
-    </row>
-    <row r="11" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="53"/>
-      <c r="B11" s="69"/>
-      <c r="C11" s="25" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="20"/>
-      <c r="G11" s="20"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="48"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="20"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="11"/>
-      <c r="U11" s="11"/>
-      <c r="V11" s="19"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10"/>
-    </row>
-    <row r="12" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="64">
-        <v>3</v>
-      </c>
-      <c r="B12" s="65" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="34">
-        <v>46064</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="M12" s="62"/>
-      <c r="N12" s="71"/>
-      <c r="O12" s="71"/>
-      <c r="P12" s="73" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q12" s="20"/>
-      <c r="R12" s="20"/>
-      <c r="S12" s="20"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-    </row>
-    <row r="13" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="53"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="72"/>
-      <c r="O13" s="72"/>
-      <c r="P13" s="74"/>
-      <c r="Q13" s="20"/>
-      <c r="R13" s="20"/>
-      <c r="S13" s="20"/>
-      <c r="T13" s="11"/>
-      <c r="U13" s="11"/>
-      <c r="V13" s="19"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10"/>
-    </row>
-    <row r="14" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="59">
-        <v>4</v>
-      </c>
-      <c r="B14" s="60" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="34">
-        <v>46338</v>
-      </c>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="20"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="20"/>
-      <c r="Q14" s="75"/>
-      <c r="R14" s="77" t="s">
-        <v>54</v>
-      </c>
-      <c r="S14" s="20"/>
-      <c r="T14" s="11"/>
-      <c r="U14" s="11"/>
-      <c r="V14" s="19"/>
-      <c r="W14" s="21"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10"/>
-    </row>
-    <row r="15" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="53"/>
-      <c r="B15" s="55"/>
-      <c r="C15" s="25" t="s">
-        <v>46</v>
+    <row r="15" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="96"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="36" t="s">
+        <v>63</v>
       </c>
       <c r="D15" s="61"/>
       <c r="E15" s="61"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="J15" s="20"/>
-      <c r="K15" s="20"/>
-      <c r="L15" s="20"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="20"/>
-      <c r="Q15" s="76"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="20"/>
-      <c r="T15" s="11"/>
-      <c r="U15" s="11"/>
-      <c r="V15" s="19"/>
-      <c r="W15" s="21"/>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="N15" s="62" t="s">
+        <v>63</v>
+      </c>
+      <c r="O15" s="63"/>
+      <c r="P15" s="64"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="13"/>
+      <c r="S15" s="13"/>
+      <c r="T15" s="10"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="8"/>
+      <c r="X15" s="9"/>
+      <c r="Y15" s="9"/>
     </row>
-    <row r="16" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="53"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="20"/>
-      <c r="Q16" s="76"/>
-      <c r="R16" s="78"/>
-      <c r="S16" s="20"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="19"/>
-      <c r="W16" s="21"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10"/>
+    <row r="16" spans="1:25" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="89">
+        <v>4</v>
+      </c>
+      <c r="B16" s="91" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="59">
+        <v>46338</v>
+      </c>
+      <c r="F16" s="27"/>
+      <c r="G16" s="13"/>
+      <c r="J16" s="13"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="13"/>
+      <c r="M16" s="20"/>
+      <c r="N16" s="11"/>
+      <c r="R16" s="97"/>
+      <c r="S16" s="44" t="s">
+        <v>52</v>
+      </c>
+      <c r="T16" s="10"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="9"/>
+      <c r="Y16" s="9"/>
     </row>
-    <row r="17" spans="1:25" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="22"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="9"/>
-      <c r="R17" s="9"/>
-      <c r="S17" s="9"/>
-      <c r="T17" s="9"/>
-      <c r="U17" s="9"/>
-      <c r="V17" s="9"/>
-      <c r="W17" s="9"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="10"/>
+    <row r="17" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="90"/>
+      <c r="B17" s="92"/>
+      <c r="C17" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="20"/>
+      <c r="N17" s="13"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="45"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="9"/>
+      <c r="Y17" s="9"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="22"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
+    <row r="18" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="90"/>
+      <c r="B18" s="93"/>
+      <c r="C18" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="82"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="13"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="45"/>
+      <c r="T18" s="10"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="9"/>
+      <c r="Y18" s="9"/>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
-      <c r="S19" s="3"/>
-      <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="8"/>
+      <c r="R19" s="8"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="8"/>
+      <c r="U19" s="8"/>
+      <c r="V19" s="8"/>
+      <c r="W19" s="8"/>
+      <c r="X19" s="9"/>
+      <c r="Y19" s="9"/>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
-      <c r="S20" s="3"/>
-      <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="17"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
@@ -1997,35 +2401,91 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3"/>
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+      <c r="U22" s="3"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="Q14:Q16"/>
-    <mergeCell ref="R14:R16"/>
-    <mergeCell ref="M12:O13"/>
-    <mergeCell ref="P12:P13"/>
-    <mergeCell ref="L8:L11"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="D14:D16"/>
-    <mergeCell ref="E14:E16"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E12:E13"/>
+  <mergeCells count="30">
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="A13:A15"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A9:A11"/>
     <mergeCell ref="D6:D7"/>
-    <mergeCell ref="B8:B11"/>
     <mergeCell ref="E6:E7"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="E9:E12"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:G7"/>
-    <mergeCell ref="J9:K11"/>
     <mergeCell ref="H8:I8"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="N15:P15"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="M8:M12"/>
+    <mergeCell ref="S16:S18"/>
+    <mergeCell ref="Q13:Q15"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="R16:R18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/C/Project/ATM_Sim/Doc/Project timeline.xlsx
+++ b/C/Project/ATM_Sim/Doc/Project timeline.xlsx
@@ -1166,95 +1166,47 @@
     <xf numFmtId="0" fontId="11" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1275,10 +1227,61 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="9" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1290,52 +1293,49 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1709,11 +1709,11 @@
   <sheetData>
     <row r="1" spans="1:25" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="1"/>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -1738,11 +1738,11 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
-      <c r="B2" s="76" t="s">
+      <c r="B2" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -1923,23 +1923,23 @@
       <c r="Y5" s="9"/>
     </row>
     <row r="6" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="77">
+      <c r="A6" s="61">
         <v>1</v>
       </c>
-      <c r="B6" s="79" t="s">
+      <c r="B6" s="63" t="s">
         <v>34</v>
       </c>
       <c r="C6" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="81" t="s">
+      <c r="D6" s="53" t="s">
         <v>36</v>
       </c>
       <c r="E6" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="70"/>
-      <c r="G6" s="72" t="s">
+      <c r="F6" s="72"/>
+      <c r="G6" s="74" t="s">
         <v>46</v>
       </c>
       <c r="H6" s="11"/>
@@ -1962,15 +1962,15 @@
       <c r="Y6" s="9"/>
     </row>
     <row r="7" spans="1:25" ht="38" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="78"/>
-      <c r="B7" s="80"/>
+      <c r="A7" s="62"/>
+      <c r="B7" s="64"/>
       <c r="C7" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="82"/>
+      <c r="D7" s="54"/>
       <c r="E7" s="66"/>
-      <c r="F7" s="71"/>
-      <c r="G7" s="73"/>
+      <c r="F7" s="73"/>
+      <c r="G7" s="75"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
@@ -1991,10 +1991,10 @@
       <c r="Y7" s="9"/>
     </row>
     <row r="8" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="86">
+      <c r="A8" s="44">
         <v>2</v>
       </c>
-      <c r="B8" s="83" t="s">
+      <c r="B8" s="84" t="s">
         <v>39</v>
       </c>
       <c r="C8" s="24" t="s">
@@ -2008,14 +2008,14 @@
       </c>
       <c r="F8" s="26"/>
       <c r="G8" s="21"/>
-      <c r="H8" s="54" t="s">
+      <c r="H8" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="55"/>
+      <c r="I8" s="77"/>
       <c r="J8" s="13"/>
       <c r="K8" s="13"/>
       <c r="L8" s="13"/>
-      <c r="M8" s="99" t="s">
+      <c r="M8" s="87" t="s">
         <v>48</v>
       </c>
       <c r="N8" s="19"/>
@@ -2032,25 +2032,25 @@
       <c r="Y8" s="9"/>
     </row>
     <row r="9" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="87"/>
-      <c r="B9" s="84"/>
+      <c r="A9" s="45"/>
+      <c r="B9" s="85"/>
       <c r="C9" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="52">
         <v>46366</v>
       </c>
-      <c r="E9" s="67" t="s">
+      <c r="E9" s="69" t="s">
         <v>49</v>
       </c>
       <c r="F9" s="27"/>
       <c r="G9" s="13"/>
-      <c r="J9" s="49" t="s">
+      <c r="J9" s="95" t="s">
         <v>61</v>
       </c>
-      <c r="K9" s="50"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="100"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="97"/>
+      <c r="M9" s="88"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
       <c r="P9" s="20"/>
@@ -2065,19 +2065,19 @@
       <c r="Y9" s="9"/>
     </row>
     <row r="10" spans="1:25" ht="38" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="87"/>
-      <c r="B10" s="84"/>
+      <c r="A10" s="45"/>
+      <c r="B10" s="85"/>
       <c r="C10" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="60"/>
-      <c r="E10" s="68"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="70"/>
       <c r="F10" s="27"/>
       <c r="G10" s="13"/>
       <c r="K10" s="43" t="s">
         <v>60</v>
       </c>
-      <c r="M10" s="101"/>
+      <c r="M10" s="89"/>
       <c r="N10" s="13"/>
       <c r="O10" s="13"/>
       <c r="P10" s="20"/>
@@ -2092,20 +2092,20 @@
       <c r="Y10" s="9"/>
     </row>
     <row r="11" spans="1:25" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="87"/>
-      <c r="B11" s="84"/>
+      <c r="A11" s="45"/>
+      <c r="B11" s="85"/>
       <c r="C11" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="60"/>
-      <c r="E11" s="68"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="70"/>
       <c r="F11" s="27"/>
       <c r="G11" s="13"/>
-      <c r="K11" s="49" t="s">
+      <c r="K11" s="95" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="51"/>
-      <c r="M11" s="101"/>
+      <c r="L11" s="97"/>
+      <c r="M11" s="89"/>
       <c r="N11" s="13"/>
       <c r="O11" s="13"/>
       <c r="P11" s="20"/>
@@ -2120,20 +2120,20 @@
       <c r="Y11" s="9"/>
     </row>
     <row r="12" spans="1:25" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="88"/>
-      <c r="B12" s="85"/>
+      <c r="A12" s="46"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="61"/>
-      <c r="E12" s="69"/>
+      <c r="D12" s="68"/>
+      <c r="E12" s="71"/>
       <c r="F12" s="27"/>
       <c r="G12" s="13"/>
-      <c r="K12" s="52" t="s">
+      <c r="K12" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="L12" s="53"/>
-      <c r="M12" s="101"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="89"/>
       <c r="N12" s="18"/>
       <c r="O12" s="18"/>
       <c r="P12" s="20"/>
@@ -2148,19 +2148,19 @@
       <c r="Y12" s="9"/>
     </row>
     <row r="13" spans="1:25" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="94">
+      <c r="A13" s="55">
         <v>3</v>
       </c>
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="78" t="s">
         <v>59</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="D13" s="59">
+      <c r="D13" s="52">
         <v>46064</v>
       </c>
-      <c r="E13" s="59" t="s">
+      <c r="E13" s="52" t="s">
         <v>55</v>
       </c>
       <c r="F13" s="27"/>
@@ -2176,7 +2176,7 @@
       <c r="P13" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="Q13" s="46" t="s">
+      <c r="Q13" s="92" t="s">
         <v>50</v>
       </c>
       <c r="R13" s="13"/>
@@ -2189,23 +2189,23 @@
       <c r="Y13" s="9"/>
     </row>
     <row r="14" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="95"/>
-      <c r="B14" s="57"/>
+      <c r="A14" s="56"/>
+      <c r="B14" s="79"/>
       <c r="C14" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="60"/>
-      <c r="E14" s="60"/>
+      <c r="D14" s="67"/>
+      <c r="E14" s="67"/>
       <c r="F14" s="27"/>
       <c r="G14" s="13"/>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
-      <c r="N14" s="62" t="s">
+      <c r="N14" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="O14" s="63"/>
-      <c r="P14" s="64"/>
-      <c r="Q14" s="47"/>
+      <c r="O14" s="82"/>
+      <c r="P14" s="83"/>
+      <c r="Q14" s="93"/>
       <c r="R14" s="13"/>
       <c r="S14" s="13"/>
       <c r="T14" s="10"/>
@@ -2216,23 +2216,23 @@
       <c r="Y14" s="9"/>
     </row>
     <row r="15" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="96"/>
-      <c r="B15" s="58"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="80"/>
       <c r="C15" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
       <c r="F15" s="27"/>
       <c r="G15" s="13"/>
       <c r="J15" s="13"/>
       <c r="K15" s="13"/>
-      <c r="N15" s="62" t="s">
+      <c r="N15" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="O15" s="63"/>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="48"/>
+      <c r="O15" s="82"/>
+      <c r="P15" s="83"/>
+      <c r="Q15" s="94"/>
       <c r="R15" s="13"/>
       <c r="S15" s="13"/>
       <c r="T15" s="10"/>
@@ -2243,19 +2243,19 @@
       <c r="Y15" s="9"/>
     </row>
     <row r="16" spans="1:25" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="89">
+      <c r="A16" s="47">
         <v>4</v>
       </c>
-      <c r="B16" s="91" t="s">
+      <c r="B16" s="49" t="s">
         <v>51</v>
       </c>
       <c r="C16" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="59" t="s">
+      <c r="D16" s="52" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="59">
+      <c r="E16" s="52">
         <v>46338</v>
       </c>
       <c r="F16" s="27"/>
@@ -2265,8 +2265,8 @@
       <c r="L16" s="13"/>
       <c r="M16" s="20"/>
       <c r="N16" s="11"/>
-      <c r="R16" s="97"/>
-      <c r="S16" s="44" t="s">
+      <c r="R16" s="100"/>
+      <c r="S16" s="90" t="s">
         <v>52</v>
       </c>
       <c r="T16" s="10"/>
@@ -2277,13 +2277,13 @@
       <c r="Y16" s="9"/>
     </row>
     <row r="17" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="90"/>
-      <c r="B17" s="92"/>
+      <c r="A17" s="48"/>
+      <c r="B17" s="50"/>
       <c r="C17" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="81"/>
-      <c r="E17" s="81"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
       <c r="F17" s="27"/>
       <c r="G17" s="13"/>
       <c r="J17" s="13"/>
@@ -2291,8 +2291,8 @@
       <c r="L17" s="13"/>
       <c r="M17" s="20"/>
       <c r="N17" s="13"/>
-      <c r="R17" s="98"/>
-      <c r="S17" s="45"/>
+      <c r="R17" s="101"/>
+      <c r="S17" s="91"/>
       <c r="T17" s="10"/>
       <c r="U17" s="10"/>
       <c r="V17" s="12"/>
@@ -2301,13 +2301,13 @@
       <c r="Y17" s="9"/>
     </row>
     <row r="18" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="90"/>
-      <c r="B18" s="93"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="51"/>
       <c r="C18" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
       <c r="F18" s="27"/>
       <c r="G18" s="13"/>
       <c r="J18" s="13"/>
@@ -2315,8 +2315,8 @@
       <c r="L18" s="13"/>
       <c r="M18" s="20"/>
       <c r="N18" s="13"/>
-      <c r="R18" s="98"/>
-      <c r="S18" s="45"/>
+      <c r="R18" s="101"/>
+      <c r="S18" s="91"/>
       <c r="T18" s="10"/>
       <c r="U18" s="10"/>
       <c r="V18" s="12"/>
@@ -2456,22 +2456,12 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="D9:D12"/>
-    <mergeCell ref="E9:E12"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="S16:S18"/>
+    <mergeCell ref="Q13:Q15"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="R16:R18"/>
     <mergeCell ref="H8:I8"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="D13:D15"/>
@@ -2480,12 +2470,22 @@
     <mergeCell ref="N15:P15"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="M8:M12"/>
-    <mergeCell ref="S16:S18"/>
-    <mergeCell ref="Q13:Q15"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="R16:R18"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="D9:D12"/>
+    <mergeCell ref="E9:E12"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
